--- a/Analysis/MetricsSummary/metrics_summary_all_models_imputed_perrun.xlsx
+++ b/Analysis/MetricsSummary/metrics_summary_all_models_imputed_perrun.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="pooled" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="imputation_counts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_run_detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="imputation_counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_run_detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,13 +477,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.144</v>
+        <v>0.12478</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -508,13 +507,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.14522</v>
+        <v>0.13128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,13 +537,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.36682</v>
+        <v>0.39078</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,13 +567,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7221</v>
+        <v>0.72922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -598,13 +597,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.23142</v>
+        <v>0.22316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -628,13 +627,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.30174</v>
+        <v>0.28436</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -658,13 +657,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3039</v>
+        <v>1.27428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -688,13 +687,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>193.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -718,13 +717,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.24066</v>
+        <v>0.2205</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -748,13 +747,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.26518</v>
+        <v>0.25374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -778,13 +777,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.19736</v>
+        <v>0.20452</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -808,13 +807,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.22242</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.30668</v>
+        <v>0.25328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -868,13 +867,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.33078</v>
+        <v>0.2695</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -898,13 +897,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.5353800000000001</v>
+        <v>0.48358</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -928,13 +927,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.8112999999999999</v>
+        <v>0.8172599999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -958,13 +957,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.16772</v>
+        <v>0.17004</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -988,13 +987,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.23652</v>
+        <v>0.23994</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1018,13 +1017,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.4102</v>
+        <v>1.41104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1048,13 +1047,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>195</v>
+        <v>194.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1078,13 +1077,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.17422</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1108,13 +1107,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.16452</v>
+        <v>0.15934</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1138,13 +1137,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.17786</v>
+        <v>0.17698</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,13 +1167,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.15426</v>
+        <v>0.16784</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1198,13 +1197,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.89732</v>
+        <v>0.8581799999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1228,13 +1227,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.9101399999999999</v>
+        <v>0.8761599999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1258,13 +1257,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.9076000000000001</v>
+        <v>0.88798</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1288,13 +1287,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.9774200000000001</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1318,13 +1317,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.04484</v>
+        <v>0.05416</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1348,13 +1347,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.09172</v>
+        <v>0.11236</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1378,13 +1377,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.04072</v>
+        <v>2.07514</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1408,13 +1407,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>194.8</v>
+        <v>194.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1438,13 +1437,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.06834</v>
+        <v>0.07999999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1468,13 +1467,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.08116</v>
+        <v>0.09613999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1498,13 +1497,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.008919999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1528,13 +1527,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.02082</v>
+        <v>0.03147999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1558,13 +1557,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.17606</v>
+        <v>0.17878</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1588,13 +1587,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.17334</v>
+        <v>0.18358</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1618,13 +1617,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.36206</v>
+        <v>0.39792</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1648,13 +1647,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.6974400000000001</v>
+        <v>0.7025400000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1678,13 +1677,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.219</v>
+        <v>0.20712</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1708,13 +1707,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.29534</v>
+        <v>0.27552</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1738,13 +1737,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.34858</v>
+        <v>1.33024</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1774,7 +1773,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1798,13 +1797,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.24774</v>
+        <v>0.2257</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1828,13 +1827,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.24838</v>
+        <v>0.2471</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1858,13 +1857,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.16834</v>
+        <v>0.15104</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1888,13 +1887,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.2116</v>
+        <v>0.20466</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1918,13 +1917,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.30986</v>
+        <v>0.29846</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1948,13 +1947,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.328</v>
+        <v>0.32102</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1978,13 +1977,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.48708</v>
+        <v>0.4748599999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2008,13 +2007,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.79582</v>
+        <v>0.7712800000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2038,13 +2037,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.15838</v>
+        <v>0.14696</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2068,13 +2067,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.23114</v>
+        <v>0.2101</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2098,13 +2097,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.45942</v>
+        <v>1.42964</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2128,13 +2127,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2158,13 +2157,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.17686</v>
+        <v>0.15456</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2188,13 +2187,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.16548</v>
+        <v>0.1508</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2218,13 +2217,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.14004</v>
+        <v>0.12786</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2248,13 +2247,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.15112</v>
+        <v>0.1547</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2278,13 +2277,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.9234399999999999</v>
+        <v>0.8912800000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2308,13 +2307,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.9348599999999999</v>
+        <v>0.9077</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2338,13 +2337,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.93126</v>
+        <v>0.90154</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2368,13 +2367,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2398,13 +2397,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.04768</v>
+        <v>0.0483</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2428,13 +2427,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.10066</v>
+        <v>0.0961</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2458,13 +2457,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.11124</v>
+        <v>1.98964</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2494,7 +2493,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2518,13 +2517,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.0698</v>
+        <v>0.07016</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2548,13 +2547,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.09211999999999999</v>
+        <v>0.09025999999999998</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2578,13 +2577,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.00906</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2608,13 +2607,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.01974</v>
+        <v>0.02394</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2638,13 +2637,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.04068000000000001</v>
+        <v>0.03248</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2668,13 +2667,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.03845999999999999</v>
+        <v>0.03795999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2698,13 +2697,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.33334</v>
+        <v>0.34052</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2728,13 +2727,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.66462</v>
+        <v>0.66562</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2758,13 +2757,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.24106</v>
+        <v>0.24648</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2788,13 +2787,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.30628</v>
+        <v>0.31242</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2818,13 +2817,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.27058</v>
+        <v>1.26754</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2854,7 +2853,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2878,13 +2877,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.25812</v>
+        <v>0.2559</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2908,13 +2907,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.2924</v>
+        <v>0.29542</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2938,13 +2937,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.18314</v>
+        <v>0.18724</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2968,13 +2967,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.2307</v>
+        <v>0.2473</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2998,13 +2997,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.2724799999999999</v>
+        <v>0.23418</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3028,13 +3027,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.29076</v>
+        <v>0.25078</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3058,13 +3057,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.47386</v>
+        <v>0.46462</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3088,13 +3087,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.7651199999999999</v>
+        <v>0.76308</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3118,13 +3117,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.16898</v>
+        <v>0.17918</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3148,13 +3147,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.24216</v>
+        <v>0.25182</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3178,13 +3177,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.43308</v>
+        <v>1.40546</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3214,7 +3213,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3238,13 +3237,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.17246</v>
+        <v>0.18016</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3268,13 +3267,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.16606</v>
+        <v>0.18258</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3298,13 +3297,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.155</v>
+        <v>0.16034</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3328,13 +3327,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.1824</v>
+        <v>0.19364</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3358,13 +3357,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.8974400000000001</v>
+        <v>0.88188</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3388,13 +3387,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.9113599999999999</v>
+        <v>0.89794</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3418,13 +3417,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.9173</v>
+        <v>0.90352</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3448,13 +3447,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.9812799999999999</v>
+        <v>0.9787399999999999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3478,13 +3477,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.05188</v>
+        <v>0.05492</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3508,13 +3507,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.10148</v>
+        <v>0.10352</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3538,13 +3537,13 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.95558</v>
+        <v>1.88496</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3568,13 +3567,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>171.6</v>
+        <v>178</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3598,13 +3597,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.07828</v>
+        <v>0.08051999999999999</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3628,13 +3627,13 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.09776</v>
+        <v>0.0992</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3658,13 +3657,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.01012</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3688,13 +3687,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.02126</v>
+        <v>0.03036</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3718,13 +3717,13 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.009980000000000001</v>
+        <v>0.00548</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3748,13 +3747,13 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.007760000000000001</v>
+        <v>-0.0005600000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3778,13 +3777,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.30012</v>
+        <v>0.31114</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3808,13 +3807,13 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.6772799999999999</v>
+        <v>0.6721600000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3838,13 +3837,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.23486</v>
+        <v>0.23774</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3868,13 +3867,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.2948</v>
+        <v>0.2988</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3898,13 +3897,13 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1.25524</v>
+        <v>1.25686</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3928,13 +3927,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>194.6</v>
+        <v>192.8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3958,13 +3957,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.25538</v>
+        <v>0.2554</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3988,13 +3987,13 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.2739</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4018,13 +4017,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.19428</v>
+        <v>0.19748</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4048,13 +4047,13 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.21586</v>
+        <v>0.22274</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4078,13 +4077,13 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.2082</v>
+        <v>0.14736</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4108,13 +4107,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.22412</v>
+        <v>0.15898</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4138,13 +4137,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.46566</v>
+        <v>0.43898</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4168,13 +4167,13 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.7805199999999999</v>
+        <v>0.73948</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4198,13 +4197,13 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.19354</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4228,13 +4227,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0.26056</v>
+        <v>0.26584</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4258,13 +4257,13 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1.3463</v>
+        <v>1.33928</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4294,7 +4293,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4318,13 +4317,13 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.19752</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4348,13 +4347,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.19466</v>
+        <v>0.19756</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4378,13 +4377,13 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.19306</v>
+        <v>0.1956</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4408,13 +4407,13 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.18888</v>
+        <v>0.19486</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4438,13 +4437,13 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.8801</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4468,13 +4467,13 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.8895199999999999</v>
+        <v>0.8517999999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4498,13 +4497,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.89724</v>
+        <v>0.8646200000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4528,13 +4527,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.96918</v>
+        <v>0.9599800000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4558,13 +4557,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.07178</v>
+        <v>0.07448</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4588,13 +4587,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.16208</v>
+        <v>0.16156</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4618,13 +4617,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2.25796</v>
+        <v>2.16992</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4648,13 +4647,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>194.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4678,13 +4677,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.1115</v>
+        <v>0.11506</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4708,13 +4707,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.14984</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4738,13 +4737,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4768,7 +4767,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.0168</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="146">
@@ -4798,7 +4797,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.14872</v>
+        <v>0.12478</v>
       </c>
     </row>
     <row r="147">
@@ -4828,7 +4827,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.14976</v>
+        <v>0.13128</v>
       </c>
     </row>
     <row r="148">
@@ -4858,7 +4857,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.37026</v>
+        <v>0.39078</v>
       </c>
     </row>
     <row r="149">
@@ -4888,7 +4887,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.7240800000000001</v>
+        <v>0.72922</v>
       </c>
     </row>
     <row r="150">
@@ -4918,7 +4917,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.23172</v>
+        <v>0.22316</v>
       </c>
     </row>
     <row r="151">
@@ -4948,7 +4947,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0.30194</v>
+        <v>0.28436</v>
       </c>
     </row>
     <row r="152">
@@ -4978,7 +4977,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1.30306</v>
+        <v>1.27428</v>
       </c>
     </row>
     <row r="153">
@@ -5038,7 +5037,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0.24066</v>
+        <v>0.2205</v>
       </c>
     </row>
     <row r="155">
@@ -5068,7 +5067,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.26564</v>
+        <v>0.25374</v>
       </c>
     </row>
     <row r="156">
@@ -5098,7 +5097,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.19818</v>
+        <v>0.20452</v>
       </c>
     </row>
     <row r="157">
@@ -5128,7 +5127,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.22242</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="158">
@@ -5158,7 +5157,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.30668</v>
+        <v>0.25402</v>
       </c>
     </row>
     <row r="159">
@@ -5188,7 +5187,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.33078</v>
+        <v>0.27026</v>
       </c>
     </row>
     <row r="160">
@@ -5218,7 +5217,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0.5353800000000001</v>
+        <v>0.4841</v>
       </c>
     </row>
     <row r="161">
@@ -5248,7 +5247,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0.8112999999999999</v>
+        <v>0.8174399999999998</v>
       </c>
     </row>
     <row r="162">
@@ -5278,7 +5277,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0.16772</v>
+        <v>0.17016</v>
       </c>
     </row>
     <row r="163">
@@ -5308,7 +5307,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.23652</v>
+        <v>0.24004</v>
       </c>
     </row>
     <row r="164">
@@ -5338,7 +5337,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1.4102</v>
+        <v>1.41064</v>
       </c>
     </row>
     <row r="165">
@@ -5398,7 +5397,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.17422</v>
+        <v>0.17616</v>
       </c>
     </row>
     <row r="167">
@@ -5428,7 +5427,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.16452</v>
+        <v>0.15966</v>
       </c>
     </row>
     <row r="168">
@@ -5458,7 +5457,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.17786</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="169">
@@ -5488,7 +5487,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.15426</v>
+        <v>0.16786</v>
       </c>
     </row>
     <row r="170">
@@ -5518,7 +5517,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.8967600000000001</v>
+        <v>0.8557399999999999</v>
       </c>
     </row>
     <row r="171">
@@ -5548,7 +5547,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0.90974</v>
+        <v>0.87334</v>
       </c>
     </row>
     <row r="172">
@@ -5578,7 +5577,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.90668</v>
+        <v>0.8861399999999999</v>
       </c>
     </row>
     <row r="173">
@@ -5608,7 +5607,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.9774600000000001</v>
+        <v>0.96716</v>
       </c>
     </row>
     <row r="174">
@@ -5638,7 +5637,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.04492</v>
+        <v>0.05472</v>
       </c>
     </row>
     <row r="175">
@@ -5668,7 +5667,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.09184</v>
+        <v>0.11328</v>
       </c>
     </row>
     <row r="176">
@@ -5698,7 +5697,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>2.03976</v>
+        <v>2.07026</v>
       </c>
     </row>
     <row r="177">
@@ -5758,7 +5757,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.06832000000000001</v>
+        <v>0.08062</v>
       </c>
     </row>
     <row r="179">
@@ -5788,7 +5787,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.09672</v>
       </c>
     </row>
     <row r="180">
@@ -5818,7 +5817,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>0.00924</v>
+        <v>0.009639999999999999</v>
       </c>
     </row>
     <row r="181">
@@ -5848,7 +5847,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.02086</v>
+        <v>0.03186</v>
       </c>
     </row>
     <row r="182">
@@ -5878,7 +5877,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0.17606</v>
+        <v>0.17878</v>
       </c>
     </row>
     <row r="183">
@@ -5908,7 +5907,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.17334</v>
+        <v>0.18358</v>
       </c>
     </row>
     <row r="184">
@@ -5938,7 +5937,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.36206</v>
+        <v>0.39792</v>
       </c>
     </row>
     <row r="185">
@@ -5968,7 +5967,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.6974400000000001</v>
+        <v>0.7025400000000001</v>
       </c>
     </row>
     <row r="186">
@@ -5998,7 +5997,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.219</v>
+        <v>0.20712</v>
       </c>
     </row>
     <row r="187">
@@ -6028,7 +6027,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>0.29534</v>
+        <v>0.27552</v>
       </c>
     </row>
     <row r="188">
@@ -6058,7 +6057,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1.34858</v>
+        <v>1.33024</v>
       </c>
     </row>
     <row r="189">
@@ -6118,7 +6117,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0.24774</v>
+        <v>0.2257</v>
       </c>
     </row>
     <row r="191">
@@ -6148,7 +6147,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0.24838</v>
+        <v>0.2471</v>
       </c>
     </row>
     <row r="192">
@@ -6178,7 +6177,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0.16834</v>
+        <v>0.15104</v>
       </c>
     </row>
     <row r="193">
@@ -6208,7 +6207,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>0.2116</v>
+        <v>0.20466</v>
       </c>
     </row>
     <row r="194">
@@ -6238,7 +6237,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.30872</v>
+        <v>0.29846</v>
       </c>
     </row>
     <row r="195">
@@ -6268,7 +6267,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.3266600000000001</v>
+        <v>0.32102</v>
       </c>
     </row>
     <row r="196">
@@ -6298,7 +6297,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>0.48822</v>
+        <v>0.4748599999999999</v>
       </c>
     </row>
     <row r="197">
@@ -6328,7 +6327,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0.7958999999999999</v>
+        <v>0.7712800000000001</v>
       </c>
     </row>
     <row r="198">
@@ -6358,7 +6357,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.15992</v>
+        <v>0.14696</v>
       </c>
     </row>
     <row r="199">
@@ -6388,7 +6387,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.23264</v>
+        <v>0.2101</v>
       </c>
     </row>
     <row r="200">
@@ -6418,7 +6417,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1.45472</v>
+        <v>1.42964</v>
       </c>
     </row>
     <row r="201">
@@ -6478,7 +6477,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.17882</v>
+        <v>0.15456</v>
       </c>
     </row>
     <row r="203">
@@ -6508,7 +6507,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>0.16762</v>
+        <v>0.1508</v>
       </c>
     </row>
     <row r="204">
@@ -6538,7 +6537,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0.1413</v>
+        <v>0.12786</v>
       </c>
     </row>
     <row r="205">
@@ -6568,7 +6567,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0.15198</v>
+        <v>0.1547</v>
       </c>
     </row>
     <row r="206">
@@ -6598,7 +6597,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.9234399999999999</v>
+        <v>0.8912800000000001</v>
       </c>
     </row>
     <row r="207">
@@ -6628,7 +6627,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>0.9348599999999999</v>
+        <v>0.9077</v>
       </c>
     </row>
     <row r="208">
@@ -6658,7 +6657,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0.93126</v>
+        <v>0.90154</v>
       </c>
     </row>
     <row r="209">
@@ -6688,7 +6687,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="210">
@@ -6718,7 +6717,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>0.04768</v>
+        <v>0.0483</v>
       </c>
     </row>
     <row r="211">
@@ -6748,7 +6747,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>0.10066</v>
+        <v>0.0961</v>
       </c>
     </row>
     <row r="212">
@@ -6778,7 +6777,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>2.11124</v>
+        <v>1.98964</v>
       </c>
     </row>
     <row r="213">
@@ -6838,7 +6837,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>0.0698</v>
+        <v>0.07016</v>
       </c>
     </row>
     <row r="215">
@@ -6868,7 +6867,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>0.09211999999999999</v>
+        <v>0.09025999999999998</v>
       </c>
     </row>
     <row r="216">
@@ -6898,7 +6897,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>0.00906</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="217">
@@ -6928,7 +6927,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>0.01974</v>
+        <v>0.02394</v>
       </c>
     </row>
     <row r="218">
@@ -6958,7 +6957,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>0.04068000000000001</v>
+        <v>0.03248</v>
       </c>
     </row>
     <row r="219">
@@ -6988,7 +6987,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0.03845999999999999</v>
+        <v>0.03795999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -7018,7 +7017,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>0.33334</v>
+        <v>0.34052</v>
       </c>
     </row>
     <row r="221">
@@ -7048,7 +7047,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>0.66462</v>
+        <v>0.66562</v>
       </c>
     </row>
     <row r="222">
@@ -7078,7 +7077,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>0.24106</v>
+        <v>0.24648</v>
       </c>
     </row>
     <row r="223">
@@ -7108,7 +7107,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>0.30628</v>
+        <v>0.31242</v>
       </c>
     </row>
     <row r="224">
@@ -7138,7 +7137,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>1.27058</v>
+        <v>1.26754</v>
       </c>
     </row>
     <row r="225">
@@ -7198,7 +7197,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>0.25812</v>
+        <v>0.2559</v>
       </c>
     </row>
     <row r="227">
@@ -7228,7 +7227,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.2924</v>
+        <v>0.29542</v>
       </c>
     </row>
     <row r="228">
@@ -7258,7 +7257,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.18314</v>
+        <v>0.18724</v>
       </c>
     </row>
     <row r="229">
@@ -7288,7 +7287,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>0.2307</v>
+        <v>0.2473</v>
       </c>
     </row>
     <row r="230">
@@ -7318,7 +7317,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.2724799999999999</v>
+        <v>0.23418</v>
       </c>
     </row>
     <row r="231">
@@ -7348,7 +7347,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>0.29076</v>
+        <v>0.25078</v>
       </c>
     </row>
     <row r="232">
@@ -7378,7 +7377,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>0.47386</v>
+        <v>0.46462</v>
       </c>
     </row>
     <row r="233">
@@ -7408,7 +7407,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.7651199999999999</v>
+        <v>0.76308</v>
       </c>
     </row>
     <row r="234">
@@ -7438,7 +7437,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>0.16898</v>
+        <v>0.17918</v>
       </c>
     </row>
     <row r="235">
@@ -7468,7 +7467,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>0.24216</v>
+        <v>0.25182</v>
       </c>
     </row>
     <row r="236">
@@ -7498,7 +7497,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>1.43308</v>
+        <v>1.40546</v>
       </c>
     </row>
     <row r="237">
@@ -7558,7 +7557,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>0.17246</v>
+        <v>0.18016</v>
       </c>
     </row>
     <row r="239">
@@ -7588,7 +7587,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>0.16606</v>
+        <v>0.18258</v>
       </c>
     </row>
     <row r="240">
@@ -7618,7 +7617,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>0.155</v>
+        <v>0.16034</v>
       </c>
     </row>
     <row r="241">
@@ -7648,7 +7647,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>0.1824</v>
+        <v>0.19364</v>
       </c>
     </row>
     <row r="242">
@@ -7678,7 +7677,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0.78666</v>
+        <v>0.7839400000000001</v>
       </c>
     </row>
     <row r="243">
@@ -7708,7 +7707,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0.7984600000000001</v>
+        <v>0.7964</v>
       </c>
     </row>
     <row r="244">
@@ -7738,7 +7737,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0.83694</v>
+        <v>0.8399800000000001</v>
       </c>
     </row>
     <row r="245">
@@ -7768,7 +7767,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0.95076</v>
+        <v>0.9497199999999999</v>
       </c>
     </row>
     <row r="246">
@@ -7798,7 +7797,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.07716000000000001</v>
+        <v>0.07166</v>
       </c>
     </row>
     <row r="247">
@@ -7828,7 +7827,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>0.14066</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="248">
@@ -7858,7 +7857,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>1.82332</v>
+        <v>1.82844</v>
       </c>
     </row>
     <row r="249">
@@ -7918,7 +7917,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0.10078</v>
+        <v>0.09626</v>
       </c>
     </row>
     <row r="251">
@@ -7948,7 +7947,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0.11766</v>
+        <v>0.11282</v>
       </c>
     </row>
     <row r="252">
@@ -7978,7 +7977,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0.04178</v>
+        <v>0.03236</v>
       </c>
     </row>
     <row r="253">
@@ -8008,7 +8007,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.0484</v>
+        <v>0.04528</v>
       </c>
     </row>
     <row r="254">
@@ -8038,7 +8037,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.01198</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="255">
@@ -8068,7 +8067,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>0.00974</v>
+        <v>-0.00308</v>
       </c>
     </row>
     <row r="256">
@@ -8098,7 +8097,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>0.30152</v>
+        <v>0.30974</v>
       </c>
     </row>
     <row r="257">
@@ -8128,7 +8127,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0.67796</v>
+        <v>0.6697599999999999</v>
       </c>
     </row>
     <row r="258">
@@ -8158,7 +8157,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0.23492</v>
+        <v>0.2384</v>
       </c>
     </row>
     <row r="259">
@@ -8188,7 +8187,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>0.29484</v>
+        <v>0.29928</v>
       </c>
     </row>
     <row r="260">
@@ -8218,7 +8217,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>1.25508</v>
+        <v>1.25538</v>
       </c>
     </row>
     <row r="261">
@@ -8278,7 +8277,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>0.25542</v>
+        <v>0.25664</v>
       </c>
     </row>
     <row r="263">
@@ -8308,7 +8307,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0.27394</v>
+        <v>0.27624</v>
       </c>
     </row>
     <row r="264">
@@ -8338,7 +8337,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.1944</v>
+        <v>0.19822</v>
       </c>
     </row>
     <row r="265">
@@ -8368,7 +8367,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>0.2159</v>
+        <v>0.2225</v>
       </c>
     </row>
     <row r="266">
@@ -8398,7 +8397,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0.2082</v>
+        <v>0.14736</v>
       </c>
     </row>
     <row r="267">
@@ -8428,7 +8427,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0.22412</v>
+        <v>0.15898</v>
       </c>
     </row>
     <row r="268">
@@ -8458,7 +8457,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0.46566</v>
+        <v>0.43898</v>
       </c>
     </row>
     <row r="269">
@@ -8488,7 +8487,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>0.7805199999999999</v>
+        <v>0.73948</v>
       </c>
     </row>
     <row r="270">
@@ -8518,7 +8517,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>0.19354</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="271">
@@ -8548,7 +8547,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>0.26056</v>
+        <v>0.26584</v>
       </c>
     </row>
     <row r="272">
@@ -8578,7 +8577,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1.3463</v>
+        <v>1.33928</v>
       </c>
     </row>
     <row r="273">
@@ -8638,7 +8637,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.19752</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="275">
@@ -8668,7 +8667,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0.19466</v>
+        <v>0.19756</v>
       </c>
     </row>
     <row r="276">
@@ -8698,7 +8697,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>0.19306</v>
+        <v>0.1956</v>
       </c>
     </row>
     <row r="277">
@@ -8728,7 +8727,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>0.18888</v>
+        <v>0.19486</v>
       </c>
     </row>
     <row r="278">
@@ -8758,7 +8757,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0.8769199999999999</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="279">
@@ -8788,7 +8787,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0.8861399999999999</v>
+        <v>0.8517999999999999</v>
       </c>
     </row>
     <row r="280">
@@ -8818,7 +8817,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.89538</v>
+        <v>0.8646200000000001</v>
       </c>
     </row>
     <row r="281">
@@ -8848,7 +8847,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>0.9682000000000001</v>
+        <v>0.9599800000000001</v>
       </c>
     </row>
     <row r="282">
@@ -8878,7 +8877,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.07211999999999999</v>
+        <v>0.07448</v>
       </c>
     </row>
     <row r="283">
@@ -8908,7 +8907,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0.16238</v>
+        <v>0.16156</v>
       </c>
     </row>
     <row r="284">
@@ -8938,7 +8937,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>2.25152</v>
+        <v>2.16992</v>
       </c>
     </row>
     <row r="285">
@@ -8998,7 +8997,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0.1118</v>
+        <v>0.11506</v>
       </c>
     </row>
     <row r="287">
@@ -9028,7 +9027,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>0.15002</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="288">
@@ -9058,7 +9057,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>0.00954</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="289">
@@ -9088,7 +9087,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>0.01718</v>
+        <v>0.0179</v>
       </c>
     </row>
   </sheetData>
@@ -9102,223 +9101,491 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>architecture</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>scenarios_imputed_mean_per_run</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ImputedPerRun</t>
+          <t>cells_imputed_mean_per_run</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>perrun_minus_A</t>
+          <t>scenarios_imputed_min</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>scenarios_imputed_max</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cells_imputed_min</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cells_imputed_max</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n_scenarios_per_run_min</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>n_scenarios_per_run_max</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>0.09268</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09436</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001680000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>195</v>
+      </c>
+      <c r="J2" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>overall_mae</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.231585</v>
+        <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.231675</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
-        <v>9.000000000000674e-05</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>195</v>
+      </c>
+      <c r="J3" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Direct_LLM_Scoring</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.340585</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.341795</v>
+        <v>4.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001209999999999989</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>195</v>
+      </c>
+      <c r="J4" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.274305</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.27402</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0002849999999999797</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>195</v>
+      </c>
+      <c r="J5" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>overall_mae</t>
-        </is>
-      </c>
       <c r="C6" t="n">
-        <v>0.172155</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.17254</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003850000000000242</v>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>195</v>
+      </c>
+      <c r="J6" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Example-Guided_LLM_Scoring</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.490495</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.49078</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002849999999999797</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>195</v>
+      </c>
+      <c r="J7" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>Direct_LLM_Scoring</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.899575</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8709450000000001</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02862999999999993</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>195</v>
+      </c>
+      <c r="J8" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>overall_mae</t>
+          <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.054045</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06047</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006425000000000007</v>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>195</v>
+      </c>
+      <c r="J9" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
-        </is>
-      </c>
       <c r="C10" t="n">
-        <v>0.91335</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8925649999999999</v>
+        <v>204</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02078500000000005</v>
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" t="n">
+        <v>168</v>
+      </c>
+      <c r="H10" t="n">
+        <v>228</v>
+      </c>
+      <c r="I10" t="n">
+        <v>195</v>
+      </c>
+      <c r="J10" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="n">
+        <v>36</v>
+      </c>
+      <c r="I11" t="n">
+        <v>195</v>
+      </c>
+      <c r="J11" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>195</v>
+      </c>
+      <c r="J12" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>195</v>
+      </c>
+      <c r="J13" t="n">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -9332,504 +9599,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>architecture</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>scenarios_imputed_mean_per_run</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cells_imputed_mean_per_run</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>scenarios_imputed_min</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>scenarios_imputed_max</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>cells_imputed_min</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>cells_imputed_max</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>n_scenarios_per_run_min</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>n_scenarios_per_run_max</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Direct_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>36</v>
-      </c>
-      <c r="I2" t="n">
-        <v>195</v>
-      </c>
-      <c r="J2" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>195</v>
-      </c>
-      <c r="J3" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I4" t="n">
-        <v>195</v>
-      </c>
-      <c r="J4" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Direct_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>195</v>
-      </c>
-      <c r="J5" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>24</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" t="n">
-        <v>36</v>
-      </c>
-      <c r="I6" t="n">
-        <v>195</v>
-      </c>
-      <c r="J6" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>gemini</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>195</v>
-      </c>
-      <c r="J7" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Direct_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>195</v>
-      </c>
-      <c r="J8" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>195</v>
-      </c>
-      <c r="J9" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>gptoss</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>280.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" t="n">
-        <v>26</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>312</v>
-      </c>
-      <c r="I10" t="n">
-        <v>195</v>
-      </c>
-      <c r="J10" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Direct_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="n">
-        <v>195</v>
-      </c>
-      <c r="J11" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Example-Guided_LLM_Scoring</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>195</v>
-      </c>
-      <c r="J12" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LLM-Parameterized_Reference_Scoring</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" t="n">
-        <v>195</v>
-      </c>
-      <c r="J13" t="n">
-        <v>195</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -9933,32 +9702,32 @@
         <v>195</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>195</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2171</v>
+        <v>0.0906</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2308</v>
+        <v>0.0897</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4256</v>
+        <v>0.359</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7538</v>
+        <v>0.7179</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2328</v>
+        <v>0.2255</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3024</v>
+        <v>0.2882</v>
       </c>
     </row>
     <row r="3">
@@ -9984,32 +9753,32 @@
         <v>195</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>195</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1043</v>
+        <v>0.1521</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1128</v>
+        <v>0.1667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3641</v>
+        <v>0.3949</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7282</v>
+        <v>0.7385</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2293</v>
+        <v>0.2243</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3006</v>
+        <v>0.2847</v>
       </c>
     </row>
     <row r="4">
@@ -10035,32 +9804,32 @@
         <v>195</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>195</v>
       </c>
       <c r="J4" t="n">
-        <v>0.135</v>
+        <v>0.159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1359</v>
+        <v>0.159</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3641</v>
+        <v>0.4205</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7128</v>
+        <v>0.7436</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2363</v>
+        <v>0.2189</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3075</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="5">
@@ -10086,32 +9855,32 @@
         <v>195</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>195</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1556</v>
+        <v>0.1248</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1462</v>
+        <v>0.1359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.359</v>
+        <v>0.4154</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7128</v>
+        <v>0.7538</v>
       </c>
       <c r="N5" t="n">
-        <v>0.231</v>
+        <v>0.2216</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2986</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="6">
@@ -10147,22 +9916,22 @@
         <v>195</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1316</v>
+        <v>0.0974</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1231</v>
+        <v>0.1051</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3385</v>
+        <v>0.3641</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7128</v>
+        <v>0.6923</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2292</v>
+        <v>0.2255</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3006</v>
+        <v>0.2863</v>
       </c>
     </row>
     <row r="7">
@@ -10188,32 +9957,32 @@
         <v>195</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>195</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3436</v>
+        <v>0.2752</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3615</v>
+        <v>0.2718</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5744</v>
+        <v>0.4974</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8051</v>
+        <v>0.8308</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1682</v>
+        <v>0.1718</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2376</v>
+        <v>0.2444</v>
       </c>
     </row>
     <row r="8">
@@ -10249,22 +10018,22 @@
         <v>195</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3368</v>
+        <v>0.3026</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3667</v>
+        <v>0.3256</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5641</v>
+        <v>0.4974</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8462</v>
+        <v>0.8205</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1667</v>
+        <v>0.1709</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2346</v>
+        <v>0.2392</v>
       </c>
     </row>
     <row r="9">
@@ -10300,22 +10069,22 @@
         <v>195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2581</v>
+        <v>0.2547</v>
       </c>
       <c r="K9" t="n">
         <v>0.2821</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4974</v>
+        <v>0.4872</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8103</v>
+        <v>0.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.168</v>
+        <v>0.1706</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2366</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="10">
@@ -10351,22 +10120,22 @@
         <v>195</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2855</v>
+        <v>0.2034</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3026</v>
+        <v>0.2103</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5282</v>
+        <v>0.4513</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7795</v>
+        <v>0.8154</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1674</v>
+        <v>0.1694</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2374</v>
+        <v>0.2375</v>
       </c>
     </row>
     <row r="11">
@@ -10402,22 +10171,22 @@
         <v>195</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3094</v>
+        <v>0.2342</v>
       </c>
       <c r="K11" t="n">
-        <v>0.341</v>
+        <v>0.2615</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5128</v>
+        <v>0.4872</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8154</v>
+        <v>0.8205</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1683</v>
+        <v>0.1681</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2364</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="12">
@@ -10453,22 +10222,22 @@
         <v>195</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9009</v>
+        <v>0.8496</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8667</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9231</v>
+        <v>0.8872</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9846</v>
+        <v>0.9641</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0395</v>
+        <v>0.0553</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0781</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="13">
@@ -10504,22 +10273,22 @@
         <v>195</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8872</v>
+        <v>0.8462</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9026</v>
+        <v>0.8641</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8923</v>
+        <v>0.8769</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9744</v>
+        <v>0.9641</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0469</v>
+        <v>0.0565</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0963</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="14">
@@ -10545,32 +10314,32 @@
         <v>195</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>195</v>
       </c>
       <c r="J14" t="n">
-        <v>0.894</v>
+        <v>0.8598</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9051</v>
+        <v>0.8769</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9026</v>
+        <v>0.8974</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9744</v>
+        <v>0.9692</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0462</v>
+        <v>0.0533</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1132</v>
       </c>
     </row>
     <row r="15">
@@ -10606,22 +10375,22 @@
         <v>195</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9043</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9179</v>
+        <v>0.8872</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9077</v>
+        <v>0.8923</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9795</v>
+        <v>0.9692</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0427</v>
+        <v>0.0539</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0839</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="16">
@@ -10657,22 +10426,22 @@
         <v>195</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8974</v>
+        <v>0.8496</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9103</v>
+        <v>0.8718</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9077</v>
+        <v>0.8769</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9744</v>
+        <v>0.9692</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0493</v>
+        <v>0.0546</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1066</v>
+        <v>0.1113</v>
       </c>
     </row>
     <row r="17">
@@ -10708,22 +10477,22 @@
         <v>195</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1897</v>
+        <v>0.1795</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>0.1846</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3846</v>
+        <v>0.4</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7026</v>
+        <v>0.6974</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2164</v>
+        <v>0.2084</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2922</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="18">
@@ -10759,22 +10528,22 @@
         <v>195</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1624</v>
+        <v>0.1692</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1513</v>
+        <v>0.1718</v>
       </c>
       <c r="L18" t="n">
-        <v>0.359</v>
+        <v>0.3897</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6718</v>
+        <v>0.6974</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2188</v>
+        <v>0.2074</v>
       </c>
       <c r="O18" t="n">
-        <v>0.296</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="19">
@@ -10810,22 +10579,22 @@
         <v>195</v>
       </c>
       <c r="J19" t="n">
-        <v>0.159</v>
+        <v>0.1521</v>
       </c>
       <c r="K19" t="n">
         <v>0.1615</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3436</v>
+        <v>0.3897</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7077</v>
+        <v>0.6923</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2198</v>
+        <v>0.207</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2961</v>
+        <v>0.2755</v>
       </c>
     </row>
     <row r="20">
@@ -10861,22 +10630,22 @@
         <v>195</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1829</v>
+        <v>0.2034</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1667</v>
+        <v>0.2026</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3641</v>
+        <v>0.4051</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6923</v>
+        <v>0.7128</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2209</v>
+        <v>0.2064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.297</v>
+        <v>0.2746</v>
       </c>
     </row>
     <row r="21">
@@ -10912,22 +10681,22 @@
         <v>195</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1863</v>
+        <v>0.1897</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1872</v>
+        <v>0.1974</v>
       </c>
       <c r="L21" t="n">
-        <v>0.359</v>
+        <v>0.4051</v>
       </c>
       <c r="M21" t="n">
         <v>0.7128</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2191</v>
+        <v>0.2064</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2954</v>
+        <v>0.2752</v>
       </c>
     </row>
     <row r="22">
@@ -10953,32 +10722,32 @@
         <v>195</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>195</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2786</v>
+        <v>0.3026</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2974</v>
+        <v>0.3256</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4667</v>
+        <v>0.4769</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8</v>
+        <v>0.7744</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1591</v>
+        <v>0.1468</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2328</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="23">
@@ -11004,32 +10773,32 @@
         <v>195</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>195</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3299</v>
+        <v>0.2923</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3513</v>
+        <v>0.3128</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5128</v>
+        <v>0.4769</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7641</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1598</v>
+        <v>0.1464</v>
       </c>
       <c r="O23" t="n">
-        <v>0.233</v>
+        <v>0.2092</v>
       </c>
     </row>
     <row r="24">
@@ -11055,32 +10824,32 @@
         <v>195</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>195</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2923</v>
+        <v>0.3094</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3128</v>
+        <v>0.3308</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4667</v>
+        <v>0.4769</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7897</v>
+        <v>0.7692</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1603</v>
+        <v>0.1467</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2331</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="25">
@@ -11106,32 +10875,32 @@
         <v>195</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>195</v>
       </c>
       <c r="J25" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.3231</v>
       </c>
-      <c r="K25" t="n">
-        <v>0.3359</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.4923</v>
+        <v>0.4564</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7795</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1591</v>
+        <v>0.1465</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2307</v>
+        <v>0.2089</v>
       </c>
     </row>
     <row r="26">
@@ -11157,32 +10926,32 @@
         <v>195</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>195</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3197</v>
+        <v>0.2889</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3359</v>
+        <v>0.3128</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5026</v>
+        <v>0.4872</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8</v>
+        <v>0.7692</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1613</v>
+        <v>0.1484</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2336</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="27">
@@ -11218,22 +10987,22 @@
         <v>195</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9214</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9333</v>
+        <v>0.9077</v>
       </c>
       <c r="L27" t="n">
-        <v>0.9282</v>
+        <v>0.8974</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0469</v>
+        <v>0.0466</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0994</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="28">
@@ -11269,22 +11038,22 @@
         <v>195</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9248</v>
+        <v>0.8838</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9359</v>
+        <v>0.9</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9333</v>
+        <v>0.8974</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0477</v>
+        <v>0.0498</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0998</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="29">
@@ -11320,22 +11089,22 @@
         <v>195</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9248</v>
+        <v>0.8974</v>
       </c>
       <c r="K29" t="n">
-        <v>0.9359</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9333</v>
+        <v>0.9077</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0471</v>
+        <v>0.0478</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1001</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="30">
@@ -11371,22 +11140,22 @@
         <v>195</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9248</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9359</v>
+        <v>0.9077</v>
       </c>
       <c r="L30" t="n">
-        <v>0.9333</v>
+        <v>0.9026</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0487</v>
+        <v>0.0497</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1025</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="31">
@@ -11422,22 +11191,22 @@
         <v>195</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9214</v>
+        <v>0.894</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9333</v>
+        <v>0.9103</v>
       </c>
       <c r="L31" t="n">
-        <v>0.9282</v>
+        <v>0.9026</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N31" t="n">
-        <v>0.048</v>
+        <v>0.0476</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1015</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="32">
@@ -11473,22 +11242,22 @@
         <v>195</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0017</v>
+        <v>0.0462</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.0103</v>
+        <v>0.0513</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3231</v>
+        <v>0.3692</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6359</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2392</v>
+        <v>0.2495</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3061</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="33">
@@ -11524,22 +11293,22 @@
         <v>195</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0291</v>
+        <v>0.0256</v>
       </c>
       <c r="K33" t="n">
         <v>0.0282</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3077</v>
+        <v>0.3231</v>
       </c>
       <c r="M33" t="n">
         <v>0.6615</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2419</v>
+        <v>0.2428</v>
       </c>
       <c r="O33" t="n">
-        <v>0.3057</v>
+        <v>0.3087</v>
       </c>
     </row>
     <row r="34">
@@ -11575,22 +11344,22 @@
         <v>195</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1077</v>
+        <v>0.0667</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1077</v>
+        <v>0.0718</v>
       </c>
       <c r="L34" t="n">
         <v>0.359</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7026</v>
+        <v>0.7077</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2389</v>
+        <v>0.2473</v>
       </c>
       <c r="O34" t="n">
-        <v>0.3041</v>
+        <v>0.3122</v>
       </c>
     </row>
     <row r="35">
@@ -11626,22 +11395,22 @@
         <v>195</v>
       </c>
       <c r="J35" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0641</v>
+        <v>0.0359</v>
       </c>
       <c r="L35" t="n">
-        <v>0.359</v>
+        <v>0.3231</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2429</v>
+        <v>0.2481</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3079</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="36">
@@ -11677,22 +11446,22 @@
         <v>195</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0017</v>
+        <v>-0.0017</v>
       </c>
       <c r="K36" t="n">
         <v>0.0026</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3179</v>
+        <v>0.3282</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6462</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2424</v>
+        <v>0.2447</v>
       </c>
       <c r="O36" t="n">
-        <v>0.3076</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="37">
@@ -11731,19 +11500,19 @@
         <v>0.2581</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2795</v>
+        <v>0.2769</v>
       </c>
       <c r="L37" t="n">
-        <v>0.441</v>
+        <v>0.5026</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7795</v>
+        <v>0.7436</v>
       </c>
       <c r="N37" t="n">
-        <v>0.171</v>
+        <v>0.1771</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2445</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="38">
@@ -11779,22 +11548,22 @@
         <v>195</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2786</v>
+        <v>0.2034</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2897</v>
+        <v>0.2179</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4821</v>
+        <v>0.4154</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7538</v>
+        <v>0.7744</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1693</v>
+        <v>0.181</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2435</v>
+        <v>0.2514</v>
       </c>
     </row>
     <row r="39">
@@ -11830,22 +11599,22 @@
         <v>195</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2581</v>
+        <v>0.2923</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2718</v>
+        <v>0.3103</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4923</v>
+        <v>0.5077</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7641</v>
+        <v>0.7846</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1665</v>
+        <v>0.1784</v>
       </c>
       <c r="O39" t="n">
-        <v>0.2373</v>
+        <v>0.2529</v>
       </c>
     </row>
     <row r="40">
@@ -11881,22 +11650,22 @@
         <v>195</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2308</v>
+        <v>0.1966</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2564</v>
+        <v>0.2103</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4667</v>
+        <v>0.4256</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7282</v>
+        <v>0.7538</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1712</v>
+        <v>0.1796</v>
       </c>
       <c r="O40" t="n">
-        <v>0.2448</v>
+        <v>0.2533</v>
       </c>
     </row>
     <row r="41">
@@ -11932,22 +11701,22 @@
         <v>195</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3368</v>
+        <v>0.2205</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3564</v>
+        <v>0.2385</v>
       </c>
       <c r="L41" t="n">
-        <v>0.4872</v>
+        <v>0.4718</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8</v>
+        <v>0.759</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1669</v>
+        <v>0.1798</v>
       </c>
       <c r="O41" t="n">
-        <v>0.2407</v>
+        <v>0.2523</v>
       </c>
     </row>
     <row r="42">
@@ -11973,32 +11742,32 @@
         <v>195</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
-        <v>300</v>
+        <v>168</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>195</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8017</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8077</v>
+        <v>0.8128</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8462</v>
+        <v>0.841</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9487</v>
+        <v>0.9538</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0776</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1406</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="43">
@@ -12024,32 +11793,32 @@
         <v>195</v>
       </c>
       <c r="F43" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>312</v>
+        <v>180</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>195</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7846</v>
+        <v>0.7641</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7974</v>
+        <v>0.7795</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8359</v>
+        <v>0.8308</v>
       </c>
       <c r="M43" t="n">
         <v>0.9436</v>
       </c>
       <c r="N43" t="n">
-        <v>0.0804</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1455</v>
+        <v>0.1316</v>
       </c>
     </row>
     <row r="44">
@@ -12075,32 +11844,32 @@
         <v>195</v>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>195</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7675</v>
+        <v>0.7846</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7744</v>
+        <v>0.7897</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8308</v>
+        <v>0.8256</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9436</v>
+        <v>0.9487</v>
       </c>
       <c r="N44" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1469</v>
+        <v>0.1304</v>
       </c>
     </row>
     <row r="45">
@@ -12126,32 +11895,32 @@
         <v>195</v>
       </c>
       <c r="F45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>195</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8154</v>
+        <v>0.7744</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8359</v>
+        <v>0.7846</v>
       </c>
       <c r="L45" t="n">
-        <v>0.8462</v>
+        <v>0.841</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9692</v>
+        <v>0.9487</v>
       </c>
       <c r="N45" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="O45" t="n">
-        <v>0.131</v>
+        <v>0.1347</v>
       </c>
     </row>
     <row r="46">
@@ -12177,32 +11946,32 @@
         <v>195</v>
       </c>
       <c r="F46" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>300</v>
+        <v>228</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>195</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7641</v>
+        <v>0.8017</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7769</v>
+        <v>0.8154</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8256</v>
+        <v>0.8615</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9487</v>
+        <v>0.9538</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0776</v>
+        <v>0.0722</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1393</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="47">
@@ -12228,32 +11997,32 @@
         <v>195</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>195</v>
       </c>
       <c r="J47" t="n">
-        <v>0.012</v>
+        <v>0.0393</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0205</v>
+        <v>0.041</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2615</v>
+        <v>0.3282</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6923</v>
+        <v>0.6513</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2375</v>
+        <v>0.236</v>
       </c>
       <c r="O47" t="n">
-        <v>0.298</v>
+        <v>0.2963</v>
       </c>
     </row>
     <row r="48">
@@ -12279,32 +12048,32 @@
         <v>195</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>195</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0256</v>
+        <v>-0.0393</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0179</v>
+        <v>-0.0487</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3282</v>
+        <v>0.2718</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6923</v>
+        <v>0.6462</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2352</v>
+        <v>0.2375</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2945</v>
+        <v>0.2995</v>
       </c>
     </row>
     <row r="49">
@@ -12330,32 +12099,32 @@
         <v>195</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>195</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0325</v>
+        <v>-0.0256</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0385</v>
+        <v>-0.0436</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3128</v>
+        <v>0.2974</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7026</v>
+        <v>0.6718</v>
       </c>
       <c r="N49" t="n">
-        <v>0.2349</v>
+        <v>0.24</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2937</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="50">
@@ -12381,32 +12150,32 @@
         <v>195</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>195</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.0564</v>
+        <v>0.0154</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.0692</v>
+        <v>0.0154</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2769</v>
+        <v>0.3231</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6462</v>
+        <v>0.6923</v>
       </c>
       <c r="N50" t="n">
-        <v>0.2348</v>
+        <v>0.2372</v>
       </c>
       <c r="O50" t="n">
-        <v>0.2942</v>
+        <v>0.2977</v>
       </c>
     </row>
     <row r="51">
@@ -12432,32 +12201,32 @@
         <v>195</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>195</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0462</v>
+        <v>0.0222</v>
       </c>
       <c r="K51" t="n">
-        <v>0.041</v>
+        <v>0.0205</v>
       </c>
       <c r="L51" t="n">
         <v>0.3282</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6564</v>
+        <v>0.6872</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2322</v>
+        <v>0.2413</v>
       </c>
       <c r="O51" t="n">
-        <v>0.2938</v>
+        <v>0.3033</v>
       </c>
     </row>
     <row r="52">
@@ -12493,22 +12262,22 @@
         <v>195</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2205</v>
+        <v>0.1658</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2308</v>
+        <v>0.1872</v>
       </c>
       <c r="L52" t="n">
         <v>0.4615</v>
       </c>
       <c r="M52" t="n">
-        <v>0.7641</v>
+        <v>0.7487</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1953</v>
+        <v>0.2028</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2631</v>
+        <v>0.2718</v>
       </c>
     </row>
     <row r="53">
@@ -12544,22 +12313,22 @@
         <v>195</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2137</v>
+        <v>0.1316</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2308</v>
+        <v>0.1487</v>
       </c>
       <c r="L53" t="n">
         <v>0.4513</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8</v>
+        <v>0.7282</v>
       </c>
       <c r="N53" t="n">
-        <v>0.1974</v>
+        <v>0.1981</v>
       </c>
       <c r="O53" t="n">
-        <v>0.2646</v>
+        <v>0.2662</v>
       </c>
     </row>
     <row r="54">
@@ -12595,22 +12364,22 @@
         <v>195</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2205</v>
+        <v>0.1077</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2385</v>
+        <v>0.1026</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4821</v>
+        <v>0.4</v>
       </c>
       <c r="M54" t="n">
-        <v>0.7744</v>
+        <v>0.7128</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1893</v>
+        <v>0.1937</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2547</v>
+        <v>0.2609</v>
       </c>
     </row>
     <row r="55">
@@ -12646,22 +12415,22 @@
         <v>195</v>
       </c>
       <c r="J55" t="n">
-        <v>0.241</v>
+        <v>0.1556</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2692</v>
+        <v>0.1718</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4821</v>
+        <v>0.4359</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8205</v>
+        <v>0.7436</v>
       </c>
       <c r="N55" t="n">
-        <v>0.1948</v>
+        <v>0.2029</v>
       </c>
       <c r="O55" t="n">
-        <v>0.2636</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="56">
@@ -12697,22 +12466,22 @@
         <v>195</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1453</v>
+        <v>0.1761</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1513</v>
+        <v>0.1846</v>
       </c>
       <c r="L56" t="n">
-        <v>0.4513</v>
+        <v>0.4462</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7436</v>
+        <v>0.7641</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1909</v>
+        <v>0.195</v>
       </c>
       <c r="O56" t="n">
-        <v>0.2568</v>
+        <v>0.2597</v>
       </c>
     </row>
     <row r="57">
@@ -12738,32 +12507,32 @@
         <v>195</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>195</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8872</v>
+        <v>0.853</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8923</v>
+        <v>0.8667</v>
       </c>
       <c r="L57" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8718</v>
       </c>
       <c r="M57" t="n">
-        <v>0.9641</v>
+        <v>0.9692</v>
       </c>
       <c r="N57" t="n">
-        <v>0.0741</v>
+        <v>0.0709</v>
       </c>
       <c r="O57" t="n">
-        <v>0.1674</v>
+        <v>0.1565</v>
       </c>
     </row>
     <row r="58">
@@ -12799,22 +12568,22 @@
         <v>195</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8803</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8897</v>
+        <v>0.8436</v>
       </c>
       <c r="L58" t="n">
-        <v>0.8923</v>
+        <v>0.8718</v>
       </c>
       <c r="M58" t="n">
-        <v>0.9692</v>
+        <v>0.9538</v>
       </c>
       <c r="N58" t="n">
-        <v>0.0692</v>
+        <v>0.0764</v>
       </c>
       <c r="O58" t="n">
-        <v>0.157</v>
+        <v>0.1661</v>
       </c>
     </row>
     <row r="59">
@@ -12850,22 +12619,22 @@
         <v>195</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8598</v>
+        <v>0.8393</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8692</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>0.8872</v>
+        <v>0.8718</v>
       </c>
       <c r="M59" t="n">
-        <v>0.959</v>
+        <v>0.9641</v>
       </c>
       <c r="N59" t="n">
-        <v>0.0731</v>
+        <v>0.074</v>
       </c>
       <c r="O59" t="n">
-        <v>0.1633</v>
+        <v>0.1634</v>
       </c>
     </row>
     <row r="60">
@@ -12891,32 +12660,32 @@
         <v>195</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>195</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8222</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8872</v>
+        <v>0.8385</v>
       </c>
       <c r="L60" t="n">
-        <v>0.8872</v>
+        <v>0.8462</v>
       </c>
       <c r="M60" t="n">
-        <v>0.9795</v>
+        <v>0.9538</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0736</v>
+        <v>0.0769</v>
       </c>
       <c r="O60" t="n">
-        <v>0.1668</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="61">
@@ -12952,28 +12721,28 @@
         <v>195</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8838</v>
+        <v>0.8359</v>
       </c>
       <c r="K61" t="n">
-        <v>0.8923</v>
+        <v>0.8538</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8974</v>
+        <v>0.8615</v>
       </c>
       <c r="M61" t="n">
-        <v>0.9692</v>
+        <v>0.959</v>
       </c>
       <c r="N61" t="n">
-        <v>0.0706</v>
+        <v>0.0742</v>
       </c>
       <c r="O61" t="n">
-        <v>0.1574</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12990,39 +12759,39 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>195</v>
       </c>
       <c r="J62" t="n">
-        <v>0.209</v>
+        <v>0.0906</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2228</v>
+        <v>0.0897</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4197</v>
+        <v>0.359</v>
       </c>
       <c r="M62" t="n">
-        <v>0.7513</v>
+        <v>0.7179</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2319</v>
+        <v>0.2255</v>
       </c>
       <c r="O62" t="n">
-        <v>0.3016</v>
+        <v>0.2882</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13039,39 +12808,39 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>195</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0997</v>
+        <v>0.1521</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1082</v>
+        <v>0.1667</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3608</v>
+        <v>0.3949</v>
       </c>
       <c r="M63" t="n">
-        <v>0.7268</v>
+        <v>0.7385</v>
       </c>
       <c r="N63" t="n">
-        <v>0.2294</v>
+        <v>0.2243</v>
       </c>
       <c r="O63" t="n">
-        <v>0.3008</v>
+        <v>0.2847</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13088,39 +12857,39 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>195</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1285</v>
+        <v>0.159</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1302</v>
+        <v>0.159</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3594</v>
+        <v>0.4205</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7083</v>
+        <v>0.7436</v>
       </c>
       <c r="N64" t="n">
-        <v>0.2356</v>
+        <v>0.2189</v>
       </c>
       <c r="O64" t="n">
-        <v>0.307</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13137,39 +12906,39 @@
         <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>195</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1512</v>
+        <v>0.1248</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1418</v>
+        <v>0.1359</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3557</v>
+        <v>0.4154</v>
       </c>
       <c r="M65" t="n">
-        <v>0.7113</v>
+        <v>0.7538</v>
       </c>
       <c r="N65" t="n">
-        <v>0.231</v>
+        <v>0.2216</v>
       </c>
       <c r="O65" t="n">
-        <v>0.2987</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13197,28 +12966,28 @@
         <v>195</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1316</v>
+        <v>0.0974</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1231</v>
+        <v>0.1051</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3385</v>
+        <v>0.3641</v>
       </c>
       <c r="M66" t="n">
-        <v>0.7128</v>
+        <v>0.6923</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2292</v>
+        <v>0.2255</v>
       </c>
       <c r="O66" t="n">
-        <v>0.3006</v>
+        <v>0.2863</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13235,39 +13004,39 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
         <v>195</v>
       </c>
       <c r="J67" t="n">
-        <v>0.3436</v>
+        <v>0.2715</v>
       </c>
       <c r="K67" t="n">
-        <v>0.3615</v>
+        <v>0.268</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5744</v>
+        <v>0.4948</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8051</v>
+        <v>0.8299</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1682</v>
+        <v>0.1712</v>
       </c>
       <c r="O67" t="n">
-        <v>0.2376</v>
+        <v>0.2439</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13295,28 +13064,28 @@
         <v>195</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3368</v>
+        <v>0.3026</v>
       </c>
       <c r="K68" t="n">
-        <v>0.3667</v>
+        <v>0.3256</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5641</v>
+        <v>0.4974</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8462</v>
+        <v>0.8205</v>
       </c>
       <c r="N68" t="n">
-        <v>0.1667</v>
+        <v>0.1709</v>
       </c>
       <c r="O68" t="n">
-        <v>0.2346</v>
+        <v>0.2392</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13344,28 +13113,28 @@
         <v>195</v>
       </c>
       <c r="J69" t="n">
-        <v>0.2581</v>
+        <v>0.2547</v>
       </c>
       <c r="K69" t="n">
         <v>0.2821</v>
       </c>
       <c r="L69" t="n">
-        <v>0.4974</v>
+        <v>0.4872</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8103</v>
+        <v>0.8</v>
       </c>
       <c r="N69" t="n">
-        <v>0.168</v>
+        <v>0.1706</v>
       </c>
       <c r="O69" t="n">
-        <v>0.2366</v>
+        <v>0.2411</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13393,28 +13162,28 @@
         <v>195</v>
       </c>
       <c r="J70" t="n">
-        <v>0.2855</v>
+        <v>0.2034</v>
       </c>
       <c r="K70" t="n">
-        <v>0.3026</v>
+        <v>0.2103</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5282</v>
+        <v>0.4513</v>
       </c>
       <c r="M70" t="n">
-        <v>0.7795</v>
+        <v>0.8154</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1674</v>
+        <v>0.1694</v>
       </c>
       <c r="O70" t="n">
-        <v>0.2374</v>
+        <v>0.2375</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13442,28 +13211,28 @@
         <v>195</v>
       </c>
       <c r="J71" t="n">
-        <v>0.3094</v>
+        <v>0.2342</v>
       </c>
       <c r="K71" t="n">
-        <v>0.341</v>
+        <v>0.2615</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5128</v>
+        <v>0.4872</v>
       </c>
       <c r="M71" t="n">
-        <v>0.8154</v>
+        <v>0.8205</v>
       </c>
       <c r="N71" t="n">
-        <v>0.1683</v>
+        <v>0.1681</v>
       </c>
       <c r="O71" t="n">
-        <v>0.2364</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13491,28 +13260,28 @@
         <v>195</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9009</v>
+        <v>0.8496</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8667</v>
       </c>
       <c r="L72" t="n">
-        <v>0.9231</v>
+        <v>0.8872</v>
       </c>
       <c r="M72" t="n">
-        <v>0.9846</v>
+        <v>0.9641</v>
       </c>
       <c r="N72" t="n">
-        <v>0.0395</v>
+        <v>0.0553</v>
       </c>
       <c r="O72" t="n">
-        <v>0.0781</v>
+        <v>0.1131</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13540,28 +13309,28 @@
         <v>195</v>
       </c>
       <c r="J73" t="n">
-        <v>0.89</v>
+        <v>0.8522</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9046</v>
+        <v>0.8711</v>
       </c>
       <c r="L73" t="n">
-        <v>0.8969</v>
+        <v>0.8814</v>
       </c>
       <c r="M73" t="n">
-        <v>0.9742</v>
+        <v>0.9639</v>
       </c>
       <c r="N73" t="n">
-        <v>0.0465</v>
+        <v>0.0551</v>
       </c>
       <c r="O73" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1162</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -13578,39 +13347,39 @@
         <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>195</v>
       </c>
       <c r="J74" t="n">
-        <v>0.894</v>
+        <v>0.866</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9051</v>
+        <v>0.884</v>
       </c>
       <c r="L74" t="n">
-        <v>0.9026</v>
+        <v>0.9021</v>
       </c>
       <c r="M74" t="n">
-        <v>0.9744</v>
+        <v>0.9691</v>
       </c>
       <c r="N74" t="n">
-        <v>0.0462</v>
+        <v>0.0519</v>
       </c>
       <c r="O74" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -13638,28 +13407,28 @@
         <v>195</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9043</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>0.9179</v>
+        <v>0.8872</v>
       </c>
       <c r="L75" t="n">
-        <v>0.9077</v>
+        <v>0.8923</v>
       </c>
       <c r="M75" t="n">
-        <v>0.9795</v>
+        <v>0.9692</v>
       </c>
       <c r="N75" t="n">
-        <v>0.0427</v>
+        <v>0.0539</v>
       </c>
       <c r="O75" t="n">
-        <v>0.0839</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -13687,28 +13456,28 @@
         <v>195</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8974</v>
+        <v>0.8496</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9103</v>
+        <v>0.8718</v>
       </c>
       <c r="L76" t="n">
-        <v>0.9077</v>
+        <v>0.8769</v>
       </c>
       <c r="M76" t="n">
-        <v>0.9744</v>
+        <v>0.9692</v>
       </c>
       <c r="N76" t="n">
-        <v>0.0493</v>
+        <v>0.0546</v>
       </c>
       <c r="O76" t="n">
-        <v>0.1066</v>
+        <v>0.1113</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -13736,28 +13505,28 @@
         <v>195</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1897</v>
+        <v>0.1795</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2</v>
+        <v>0.1846</v>
       </c>
       <c r="L77" t="n">
-        <v>0.3846</v>
+        <v>0.4</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7026</v>
+        <v>0.6974</v>
       </c>
       <c r="N77" t="n">
-        <v>0.2164</v>
+        <v>0.2084</v>
       </c>
       <c r="O77" t="n">
-        <v>0.2922</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -13785,28 +13554,28 @@
         <v>195</v>
       </c>
       <c r="J78" t="n">
-        <v>0.1624</v>
+        <v>0.1692</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1513</v>
+        <v>0.1718</v>
       </c>
       <c r="L78" t="n">
-        <v>0.359</v>
+        <v>0.3897</v>
       </c>
       <c r="M78" t="n">
-        <v>0.6718</v>
+        <v>0.6974</v>
       </c>
       <c r="N78" t="n">
-        <v>0.2188</v>
+        <v>0.2074</v>
       </c>
       <c r="O78" t="n">
-        <v>0.296</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -13834,28 +13603,28 @@
         <v>195</v>
       </c>
       <c r="J79" t="n">
-        <v>0.159</v>
+        <v>0.1521</v>
       </c>
       <c r="K79" t="n">
         <v>0.1615</v>
       </c>
       <c r="L79" t="n">
-        <v>0.3436</v>
+        <v>0.3897</v>
       </c>
       <c r="M79" t="n">
-        <v>0.7077</v>
+        <v>0.6923</v>
       </c>
       <c r="N79" t="n">
-        <v>0.2198</v>
+        <v>0.207</v>
       </c>
       <c r="O79" t="n">
-        <v>0.2961</v>
+        <v>0.2755</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -13883,28 +13652,28 @@
         <v>195</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1829</v>
+        <v>0.2034</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1667</v>
+        <v>0.2026</v>
       </c>
       <c r="L80" t="n">
-        <v>0.3641</v>
+        <v>0.4051</v>
       </c>
       <c r="M80" t="n">
-        <v>0.6923</v>
+        <v>0.7128</v>
       </c>
       <c r="N80" t="n">
-        <v>0.2209</v>
+        <v>0.2064</v>
       </c>
       <c r="O80" t="n">
-        <v>0.297</v>
+        <v>0.2746</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -13932,28 +13701,28 @@
         <v>195</v>
       </c>
       <c r="J81" t="n">
-        <v>0.1863</v>
+        <v>0.1897</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1872</v>
+        <v>0.1974</v>
       </c>
       <c r="L81" t="n">
-        <v>0.359</v>
+        <v>0.4051</v>
       </c>
       <c r="M81" t="n">
         <v>0.7128</v>
       </c>
       <c r="N81" t="n">
-        <v>0.2191</v>
+        <v>0.2064</v>
       </c>
       <c r="O81" t="n">
-        <v>0.2954</v>
+        <v>0.2752</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -13970,39 +13739,39 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>195</v>
       </c>
       <c r="J82" t="n">
-        <v>0.2852</v>
+        <v>0.3026</v>
       </c>
       <c r="K82" t="n">
-        <v>0.3041</v>
+        <v>0.3256</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4691</v>
+        <v>0.4769</v>
       </c>
       <c r="M82" t="n">
-        <v>0.8041</v>
+        <v>0.7744</v>
       </c>
       <c r="N82" t="n">
-        <v>0.1587</v>
+        <v>0.1468</v>
       </c>
       <c r="O82" t="n">
-        <v>0.2327</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -14019,39 +13788,39 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>195</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3299</v>
+        <v>0.2923</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3523</v>
+        <v>0.3128</v>
       </c>
       <c r="L83" t="n">
-        <v>0.513</v>
+        <v>0.4769</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7927</v>
+        <v>0.7641</v>
       </c>
       <c r="N83" t="n">
-        <v>0.1575</v>
+        <v>0.1464</v>
       </c>
       <c r="O83" t="n">
-        <v>0.2307</v>
+        <v>0.2092</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14068,39 +13837,39 @@
         <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>195</v>
       </c>
       <c r="J84" t="n">
-        <v>0.2953</v>
+        <v>0.3094</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3161</v>
+        <v>0.3308</v>
       </c>
       <c r="L84" t="n">
-        <v>0.4663</v>
+        <v>0.4769</v>
       </c>
       <c r="M84" t="n">
-        <v>0.7927</v>
+        <v>0.7692</v>
       </c>
       <c r="N84" t="n">
-        <v>0.1586</v>
+        <v>0.1467</v>
       </c>
       <c r="O84" t="n">
-        <v>0.2312</v>
+        <v>0.2094</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -14117,39 +13886,39 @@
         <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>195</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3195</v>
+        <v>0.2991</v>
       </c>
       <c r="K85" t="n">
-        <v>0.3316</v>
+        <v>0.3231</v>
       </c>
       <c r="L85" t="n">
-        <v>0.487</v>
+        <v>0.4564</v>
       </c>
       <c r="M85" t="n">
-        <v>0.7927</v>
+        <v>0.7795</v>
       </c>
       <c r="N85" t="n">
-        <v>0.1572</v>
+        <v>0.1465</v>
       </c>
       <c r="O85" t="n">
-        <v>0.2283</v>
+        <v>0.2089</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -14166,39 +13935,39 @@
         <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>195</v>
       </c>
       <c r="J86" t="n">
-        <v>0.3194</v>
+        <v>0.2889</v>
       </c>
       <c r="K86" t="n">
-        <v>0.3359</v>
+        <v>0.3128</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5</v>
+        <v>0.4872</v>
       </c>
       <c r="M86" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7692</v>
       </c>
       <c r="N86" t="n">
-        <v>0.1599</v>
+        <v>0.1484</v>
       </c>
       <c r="O86" t="n">
-        <v>0.2328</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -14226,28 +13995,28 @@
         <v>195</v>
       </c>
       <c r="J87" t="n">
-        <v>0.9214</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9333</v>
+        <v>0.9077</v>
       </c>
       <c r="L87" t="n">
-        <v>0.9282</v>
+        <v>0.8974</v>
       </c>
       <c r="M87" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N87" t="n">
-        <v>0.0469</v>
+        <v>0.0466</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0994</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -14275,28 +14044,28 @@
         <v>195</v>
       </c>
       <c r="J88" t="n">
-        <v>0.9248</v>
+        <v>0.8838</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9359</v>
+        <v>0.9</v>
       </c>
       <c r="L88" t="n">
-        <v>0.9333</v>
+        <v>0.8974</v>
       </c>
       <c r="M88" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N88" t="n">
-        <v>0.0477</v>
+        <v>0.0498</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0998</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -14324,28 +14093,28 @@
         <v>195</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9248</v>
+        <v>0.8974</v>
       </c>
       <c r="K89" t="n">
-        <v>0.9359</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="L89" t="n">
-        <v>0.9333</v>
+        <v>0.9077</v>
       </c>
       <c r="M89" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N89" t="n">
-        <v>0.0471</v>
+        <v>0.0478</v>
       </c>
       <c r="O89" t="n">
-        <v>0.1001</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -14373,28 +14142,28 @@
         <v>195</v>
       </c>
       <c r="J90" t="n">
-        <v>0.9248</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="K90" t="n">
-        <v>0.9359</v>
+        <v>0.9077</v>
       </c>
       <c r="L90" t="n">
-        <v>0.9333</v>
+        <v>0.9026</v>
       </c>
       <c r="M90" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N90" t="n">
-        <v>0.0487</v>
+        <v>0.0497</v>
       </c>
       <c r="O90" t="n">
-        <v>0.1025</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -14422,28 +14191,28 @@
         <v>195</v>
       </c>
       <c r="J91" t="n">
-        <v>0.9214</v>
+        <v>0.894</v>
       </c>
       <c r="K91" t="n">
-        <v>0.9333</v>
+        <v>0.9103</v>
       </c>
       <c r="L91" t="n">
-        <v>0.9282</v>
+        <v>0.9026</v>
       </c>
       <c r="M91" t="n">
-        <v>0.9846</v>
+        <v>0.9795</v>
       </c>
       <c r="N91" t="n">
-        <v>0.048</v>
+        <v>0.0476</v>
       </c>
       <c r="O91" t="n">
-        <v>0.1015</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -14471,28 +14240,28 @@
         <v>195</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0017</v>
+        <v>0.0462</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.0103</v>
+        <v>0.0513</v>
       </c>
       <c r="L92" t="n">
-        <v>0.3231</v>
+        <v>0.3692</v>
       </c>
       <c r="M92" t="n">
-        <v>0.6359</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="N92" t="n">
-        <v>0.2392</v>
+        <v>0.2495</v>
       </c>
       <c r="O92" t="n">
-        <v>0.3061</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -14520,28 +14289,28 @@
         <v>195</v>
       </c>
       <c r="J93" t="n">
-        <v>0.0291</v>
+        <v>0.0256</v>
       </c>
       <c r="K93" t="n">
         <v>0.0282</v>
       </c>
       <c r="L93" t="n">
-        <v>0.3077</v>
+        <v>0.3231</v>
       </c>
       <c r="M93" t="n">
         <v>0.6615</v>
       </c>
       <c r="N93" t="n">
-        <v>0.2419</v>
+        <v>0.2428</v>
       </c>
       <c r="O93" t="n">
-        <v>0.3057</v>
+        <v>0.3087</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -14569,28 +14338,28 @@
         <v>195</v>
       </c>
       <c r="J94" t="n">
-        <v>0.1077</v>
+        <v>0.0667</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1077</v>
+        <v>0.0718</v>
       </c>
       <c r="L94" t="n">
         <v>0.359</v>
       </c>
       <c r="M94" t="n">
-        <v>0.7026</v>
+        <v>0.7077</v>
       </c>
       <c r="N94" t="n">
-        <v>0.2389</v>
+        <v>0.2473</v>
       </c>
       <c r="O94" t="n">
-        <v>0.3041</v>
+        <v>0.3122</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -14618,28 +14387,28 @@
         <v>195</v>
       </c>
       <c r="J95" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0641</v>
+        <v>0.0359</v>
       </c>
       <c r="L95" t="n">
-        <v>0.359</v>
+        <v>0.3231</v>
       </c>
       <c r="M95" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="N95" t="n">
-        <v>0.2429</v>
+        <v>0.2481</v>
       </c>
       <c r="O95" t="n">
-        <v>0.3079</v>
+        <v>0.3129</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -14667,28 +14436,28 @@
         <v>195</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0017</v>
+        <v>-0.0017</v>
       </c>
       <c r="K96" t="n">
         <v>0.0026</v>
       </c>
       <c r="L96" t="n">
-        <v>0.3179</v>
+        <v>0.3282</v>
       </c>
       <c r="M96" t="n">
-        <v>0.6462</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="N96" t="n">
-        <v>0.2424</v>
+        <v>0.2447</v>
       </c>
       <c r="O96" t="n">
-        <v>0.3076</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -14719,25 +14488,25 @@
         <v>0.2581</v>
       </c>
       <c r="K97" t="n">
-        <v>0.2795</v>
+        <v>0.2769</v>
       </c>
       <c r="L97" t="n">
-        <v>0.441</v>
+        <v>0.5026</v>
       </c>
       <c r="M97" t="n">
-        <v>0.7795</v>
+        <v>0.7436</v>
       </c>
       <c r="N97" t="n">
-        <v>0.171</v>
+        <v>0.1771</v>
       </c>
       <c r="O97" t="n">
-        <v>0.2445</v>
+        <v>0.2492</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -14765,28 +14534,28 @@
         <v>195</v>
       </c>
       <c r="J98" t="n">
-        <v>0.2786</v>
+        <v>0.2034</v>
       </c>
       <c r="K98" t="n">
-        <v>0.2897</v>
+        <v>0.2179</v>
       </c>
       <c r="L98" t="n">
-        <v>0.4821</v>
+        <v>0.4154</v>
       </c>
       <c r="M98" t="n">
-        <v>0.7538</v>
+        <v>0.7744</v>
       </c>
       <c r="N98" t="n">
-        <v>0.1693</v>
+        <v>0.181</v>
       </c>
       <c r="O98" t="n">
-        <v>0.2435</v>
+        <v>0.2514</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -14814,28 +14583,28 @@
         <v>195</v>
       </c>
       <c r="J99" t="n">
-        <v>0.2581</v>
+        <v>0.2923</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2718</v>
+        <v>0.3103</v>
       </c>
       <c r="L99" t="n">
-        <v>0.4923</v>
+        <v>0.5077</v>
       </c>
       <c r="M99" t="n">
-        <v>0.7641</v>
+        <v>0.7846</v>
       </c>
       <c r="N99" t="n">
-        <v>0.1665</v>
+        <v>0.1784</v>
       </c>
       <c r="O99" t="n">
-        <v>0.2373</v>
+        <v>0.2529</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -14863,28 +14632,28 @@
         <v>195</v>
       </c>
       <c r="J100" t="n">
-        <v>0.2308</v>
+        <v>0.1966</v>
       </c>
       <c r="K100" t="n">
-        <v>0.2564</v>
+        <v>0.2103</v>
       </c>
       <c r="L100" t="n">
-        <v>0.4667</v>
+        <v>0.4256</v>
       </c>
       <c r="M100" t="n">
-        <v>0.7282</v>
+        <v>0.7538</v>
       </c>
       <c r="N100" t="n">
-        <v>0.1712</v>
+        <v>0.1796</v>
       </c>
       <c r="O100" t="n">
-        <v>0.2448</v>
+        <v>0.2533</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -14912,28 +14681,28 @@
         <v>195</v>
       </c>
       <c r="J101" t="n">
-        <v>0.3368</v>
+        <v>0.2205</v>
       </c>
       <c r="K101" t="n">
-        <v>0.3564</v>
+        <v>0.2385</v>
       </c>
       <c r="L101" t="n">
-        <v>0.4872</v>
+        <v>0.4718</v>
       </c>
       <c r="M101" t="n">
-        <v>0.8</v>
+        <v>0.759</v>
       </c>
       <c r="N101" t="n">
-        <v>0.1669</v>
+        <v>0.1798</v>
       </c>
       <c r="O101" t="n">
-        <v>0.2407</v>
+        <v>0.2523</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -14950,39 +14719,39 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I102" t="n">
         <v>195</v>
       </c>
       <c r="J102" t="n">
-        <v>0.9059</v>
+        <v>0.8637</v>
       </c>
       <c r="K102" t="n">
-        <v>0.9147</v>
+        <v>0.884</v>
       </c>
       <c r="L102" t="n">
-        <v>0.9294</v>
+        <v>0.8895</v>
       </c>
       <c r="M102" t="n">
-        <v>0.9706</v>
+        <v>0.9724</v>
       </c>
       <c r="N102" t="n">
-        <v>0.0509</v>
+        <v>0.0559</v>
       </c>
       <c r="O102" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -14999,39 +14768,39 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I103" t="n">
         <v>195</v>
       </c>
       <c r="J103" t="n">
-        <v>0.8974</v>
+        <v>0.8519</v>
       </c>
       <c r="K103" t="n">
-        <v>0.9112</v>
+        <v>0.8722</v>
       </c>
       <c r="L103" t="n">
-        <v>0.9172</v>
+        <v>0.8833</v>
       </c>
       <c r="M103" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9722</v>
       </c>
       <c r="N103" t="n">
-        <v>0.0514</v>
+        <v>0.0558</v>
       </c>
       <c r="O103" t="n">
-        <v>0.1016</v>
+        <v>0.1042</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -15048,39 +14817,39 @@
         <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I104" t="n">
         <v>195</v>
       </c>
       <c r="J104" t="n">
-        <v>0.8966</v>
+        <v>0.9091</v>
       </c>
       <c r="K104" t="n">
-        <v>0.908</v>
+        <v>0.9205</v>
       </c>
       <c r="L104" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9034</v>
       </c>
       <c r="M104" t="n">
-        <v>0.9828</v>
+        <v>0.983</v>
       </c>
       <c r="N104" t="n">
-        <v>0.0545</v>
+        <v>0.0529</v>
       </c>
       <c r="O104" t="n">
-        <v>0.1089</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -15097,39 +14866,39 @@
         <v>4</v>
       </c>
       <c r="E105" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I105" t="n">
         <v>195</v>
       </c>
       <c r="J105" t="n">
-        <v>0.901</v>
+        <v>0.8908</v>
       </c>
       <c r="K105" t="n">
-        <v>0.92</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="L105" t="n">
-        <v>0.9143</v>
+        <v>0.9153</v>
       </c>
       <c r="M105" t="n">
-        <v>0.9943</v>
+        <v>0.9831</v>
       </c>
       <c r="N105" t="n">
-        <v>0.051</v>
+        <v>0.0554</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0989</v>
+        <v>0.1049</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -15146,39 +14915,39 @@
         <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I106" t="n">
         <v>195</v>
       </c>
       <c r="J106" t="n">
-        <v>0.8863</v>
+        <v>0.8939</v>
       </c>
       <c r="K106" t="n">
-        <v>0.9029</v>
+        <v>0.9062</v>
       </c>
       <c r="L106" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9261</v>
       </c>
       <c r="M106" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.983</v>
       </c>
       <c r="N106" t="n">
-        <v>0.0516</v>
+        <v>0.0546</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0984</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -15195,39 +14964,39 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" t="n">
         <v>195</v>
       </c>
       <c r="J107" t="n">
-        <v>0.012</v>
+        <v>0.0397</v>
       </c>
       <c r="K107" t="n">
-        <v>0.0205</v>
+        <v>0.0415</v>
       </c>
       <c r="L107" t="n">
-        <v>0.2615</v>
+        <v>0.3264</v>
       </c>
       <c r="M107" t="n">
-        <v>0.6923</v>
+        <v>0.6528</v>
       </c>
       <c r="N107" t="n">
-        <v>0.2375</v>
+        <v>0.2354</v>
       </c>
       <c r="O107" t="n">
-        <v>0.298</v>
+        <v>0.2959</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -15244,39 +15013,39 @@
         <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
         <v>195</v>
       </c>
       <c r="J108" t="n">
-        <v>0.0256</v>
+        <v>-0.0382</v>
       </c>
       <c r="K108" t="n">
-        <v>0.0179</v>
+        <v>-0.0495</v>
       </c>
       <c r="L108" t="n">
-        <v>0.3282</v>
+        <v>0.276</v>
       </c>
       <c r="M108" t="n">
-        <v>0.6923</v>
+        <v>0.6458</v>
       </c>
       <c r="N108" t="n">
-        <v>0.2352</v>
+        <v>0.2353</v>
       </c>
       <c r="O108" t="n">
-        <v>0.2945</v>
+        <v>0.2977</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -15293,39 +15062,39 @@
         <v>3</v>
       </c>
       <c r="E109" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109" t="n">
         <v>195</v>
       </c>
       <c r="J109" t="n">
-        <v>0.0275</v>
+        <v>-0.0328</v>
       </c>
       <c r="K109" t="n">
-        <v>0.0335</v>
+        <v>-0.0518</v>
       </c>
       <c r="L109" t="n">
-        <v>0.3093</v>
+        <v>0.2953</v>
       </c>
       <c r="M109" t="n">
-        <v>0.701</v>
+        <v>0.6684</v>
       </c>
       <c r="N109" t="n">
-        <v>0.2342</v>
+        <v>0.2401</v>
       </c>
       <c r="O109" t="n">
-        <v>0.293</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -15342,39 +15111,39 @@
         <v>4</v>
       </c>
       <c r="E110" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110" t="n">
         <v>195</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.0564</v>
+        <v>0.0259</v>
       </c>
       <c r="K110" t="n">
-        <v>-0.0692</v>
+        <v>0.0259</v>
       </c>
       <c r="L110" t="n">
-        <v>0.2769</v>
+        <v>0.3264</v>
       </c>
       <c r="M110" t="n">
-        <v>0.6462</v>
+        <v>0.6995</v>
       </c>
       <c r="N110" t="n">
-        <v>0.2348</v>
+        <v>0.2373</v>
       </c>
       <c r="O110" t="n">
-        <v>0.2942</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -15391,39 +15160,39 @@
         <v>5</v>
       </c>
       <c r="E111" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111" t="n">
         <v>195</v>
       </c>
       <c r="J111" t="n">
-        <v>0.0412</v>
+        <v>0.0328</v>
       </c>
       <c r="K111" t="n">
-        <v>0.0361</v>
+        <v>0.0311</v>
       </c>
       <c r="L111" t="n">
-        <v>0.3247</v>
+        <v>0.3316</v>
       </c>
       <c r="M111" t="n">
-        <v>0.6546</v>
+        <v>0.6943</v>
       </c>
       <c r="N111" t="n">
-        <v>0.2326</v>
+        <v>0.2406</v>
       </c>
       <c r="O111" t="n">
-        <v>0.2943</v>
+        <v>0.3028</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -15451,28 +15220,28 @@
         <v>195</v>
       </c>
       <c r="J112" t="n">
-        <v>0.2205</v>
+        <v>0.1658</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2308</v>
+        <v>0.1872</v>
       </c>
       <c r="L112" t="n">
         <v>0.4615</v>
       </c>
       <c r="M112" t="n">
-        <v>0.7641</v>
+        <v>0.7487</v>
       </c>
       <c r="N112" t="n">
-        <v>0.1953</v>
+        <v>0.2028</v>
       </c>
       <c r="O112" t="n">
-        <v>0.2631</v>
+        <v>0.2718</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15500,28 +15269,28 @@
         <v>195</v>
       </c>
       <c r="J113" t="n">
-        <v>0.2137</v>
+        <v>0.1316</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2308</v>
+        <v>0.1487</v>
       </c>
       <c r="L113" t="n">
         <v>0.4513</v>
       </c>
       <c r="M113" t="n">
-        <v>0.8</v>
+        <v>0.7282</v>
       </c>
       <c r="N113" t="n">
-        <v>0.1974</v>
+        <v>0.1981</v>
       </c>
       <c r="O113" t="n">
-        <v>0.2646</v>
+        <v>0.2662</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15549,28 +15318,28 @@
         <v>195</v>
       </c>
       <c r="J114" t="n">
-        <v>0.2205</v>
+        <v>0.1077</v>
       </c>
       <c r="K114" t="n">
-        <v>0.2385</v>
+        <v>0.1026</v>
       </c>
       <c r="L114" t="n">
-        <v>0.4821</v>
+        <v>0.4</v>
       </c>
       <c r="M114" t="n">
-        <v>0.7744</v>
+        <v>0.7128</v>
       </c>
       <c r="N114" t="n">
-        <v>0.1893</v>
+        <v>0.1937</v>
       </c>
       <c r="O114" t="n">
-        <v>0.2547</v>
+        <v>0.2609</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15598,28 +15367,28 @@
         <v>195</v>
       </c>
       <c r="J115" t="n">
-        <v>0.241</v>
+        <v>0.1556</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2692</v>
+        <v>0.1718</v>
       </c>
       <c r="L115" t="n">
-        <v>0.4821</v>
+        <v>0.4359</v>
       </c>
       <c r="M115" t="n">
-        <v>0.8205</v>
+        <v>0.7436</v>
       </c>
       <c r="N115" t="n">
-        <v>0.1948</v>
+        <v>0.2029</v>
       </c>
       <c r="O115" t="n">
-        <v>0.2636</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15647,28 +15416,28 @@
         <v>195</v>
       </c>
       <c r="J116" t="n">
-        <v>0.1453</v>
+        <v>0.1761</v>
       </c>
       <c r="K116" t="n">
-        <v>0.1513</v>
+        <v>0.1846</v>
       </c>
       <c r="L116" t="n">
-        <v>0.4513</v>
+        <v>0.4462</v>
       </c>
       <c r="M116" t="n">
-        <v>0.7436</v>
+        <v>0.7641</v>
       </c>
       <c r="N116" t="n">
-        <v>0.1909</v>
+        <v>0.195</v>
       </c>
       <c r="O116" t="n">
-        <v>0.2568</v>
+        <v>0.2597</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15685,39 +15454,39 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>195</v>
       </c>
       <c r="J117" t="n">
-        <v>0.8969</v>
+        <v>0.853</v>
       </c>
       <c r="K117" t="n">
-        <v>0.9021</v>
+        <v>0.8667</v>
       </c>
       <c r="L117" t="n">
-        <v>0.9175</v>
+        <v>0.8718</v>
       </c>
       <c r="M117" t="n">
-        <v>0.9691</v>
+        <v>0.9692</v>
       </c>
       <c r="N117" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="O117" t="n">
-        <v>0.1661</v>
+        <v>0.1565</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -15745,28 +15514,28 @@
         <v>195</v>
       </c>
       <c r="J118" t="n">
-        <v>0.8803</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="K118" t="n">
-        <v>0.8897</v>
+        <v>0.8436</v>
       </c>
       <c r="L118" t="n">
-        <v>0.8923</v>
+        <v>0.8718</v>
       </c>
       <c r="M118" t="n">
-        <v>0.9692</v>
+        <v>0.9538</v>
       </c>
       <c r="N118" t="n">
-        <v>0.0692</v>
+        <v>0.0764</v>
       </c>
       <c r="O118" t="n">
-        <v>0.157</v>
+        <v>0.1661</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -15794,28 +15563,28 @@
         <v>195</v>
       </c>
       <c r="J119" t="n">
-        <v>0.8598</v>
+        <v>0.8393</v>
       </c>
       <c r="K119" t="n">
-        <v>0.8692</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="L119" t="n">
-        <v>0.8872</v>
+        <v>0.8718</v>
       </c>
       <c r="M119" t="n">
-        <v>0.959</v>
+        <v>0.9641</v>
       </c>
       <c r="N119" t="n">
-        <v>0.0731</v>
+        <v>0.074</v>
       </c>
       <c r="O119" t="n">
-        <v>0.1633</v>
+        <v>0.1634</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15832,39 +15601,39 @@
         <v>4</v>
       </c>
       <c r="E120" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
         <v>195</v>
       </c>
       <c r="J120" t="n">
-        <v>0.8797</v>
+        <v>0.8222</v>
       </c>
       <c r="K120" t="n">
-        <v>0.8943</v>
+        <v>0.8385</v>
       </c>
       <c r="L120" t="n">
-        <v>0.8918</v>
+        <v>0.8462</v>
       </c>
       <c r="M120" t="n">
-        <v>0.9794</v>
+        <v>0.9538</v>
       </c>
       <c r="N120" t="n">
-        <v>0.0731</v>
+        <v>0.0769</v>
       </c>
       <c r="O120" t="n">
-        <v>0.1666</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MethodA</t>
+          <t>ScoredOnly_sensitivity</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15892,22 +15661,22 @@
         <v>195</v>
       </c>
       <c r="J121" t="n">
-        <v>0.8838</v>
+        <v>0.8359</v>
       </c>
       <c r="K121" t="n">
-        <v>0.8923</v>
+        <v>0.8538</v>
       </c>
       <c r="L121" t="n">
-        <v>0.8974</v>
+        <v>0.8615</v>
       </c>
       <c r="M121" t="n">
-        <v>0.9692</v>
+        <v>0.959</v>
       </c>
       <c r="N121" t="n">
-        <v>0.0706</v>
+        <v>0.0742</v>
       </c>
       <c r="O121" t="n">
-        <v>0.1574</v>
+        <v>0.1596</v>
       </c>
     </row>
   </sheetData>
